--- a/data/FLASHDATA.xlsx
+++ b/data/FLASHDATA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ea4a19649b5fa823/Documentos/TRABAJO/MEGALO/SELLOUT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="385" documentId="8_{C3317094-D1AE-460E-929D-967AB545A9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39995D27-4D49-4756-B8B1-543F2EA2BB11}"/>
+  <xr:revisionPtr revIDLastSave="390" documentId="8_{C3317094-D1AE-460E-929D-967AB545A9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19B990E7-3F32-404E-833E-FFB6A4280043}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{5D44D5E2-3973-43DE-99E3-A9834A1BD85C}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5D44D5E2-3973-43DE-99E3-A9834A1BD85C}"/>
   </bookViews>
   <sheets>
     <sheet name="FLASHDATA" sheetId="1" r:id="rId1"/>
@@ -291,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -325,6 +325,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -754,14 +759,16 @@
       <c r="J3" s="2">
         <v>12200</v>
       </c>
-      <c r="K3" s="2"/>
+      <c r="K3" s="2">
+        <v>12000</v>
+      </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="3">
-        <f t="shared" ref="P3:P10" si="0">SUM(D3:O3)</f>
-        <v>69900</v>
+        <f>SUM(D3:O3)</f>
+        <v>81900</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -795,27 +802,29 @@
       <c r="J4" s="2">
         <v>9300</v>
       </c>
-      <c r="K4" s="2"/>
+      <c r="K4" s="2">
+        <v>10600</v>
+      </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="3">
-        <f t="shared" si="0"/>
-        <v>58400</v>
+        <f>SUM(D4:O4)</f>
+        <v>69000</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="17">
         <v>18309</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="19">
         <v>4400</v>
       </c>
       <c r="E5" s="2">
@@ -830,20 +839,22 @@
       <c r="H5" s="2">
         <v>7500</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="19">
         <v>3800</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="19">
         <v>4400</v>
       </c>
-      <c r="K5" s="2"/>
+      <c r="K5" s="2">
+        <v>4700</v>
+      </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="3">
-        <f t="shared" si="0"/>
-        <v>29100</v>
+        <f>SUM(D5:O5)</f>
+        <v>33800</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -877,14 +888,16 @@
       <c r="J6" s="2">
         <v>2500</v>
       </c>
-      <c r="K6" s="2"/>
+      <c r="K6" s="2">
+        <v>3200</v>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="3">
-        <f t="shared" si="0"/>
-        <v>18800</v>
+        <f>SUM(D6:O6)</f>
+        <v>22000</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -918,14 +931,16 @@
       <c r="J7" s="2">
         <v>900</v>
       </c>
-      <c r="K7" s="2"/>
+      <c r="K7" s="2">
+        <v>1500</v>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="3">
-        <f t="shared" si="0"/>
-        <v>7300</v>
+        <f>SUM(D7:O7)</f>
+        <v>8800</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -959,14 +974,16 @@
       <c r="J8">
         <v>700</v>
       </c>
-      <c r="K8" s="2"/>
+      <c r="K8" s="2">
+        <v>1100</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="3">
-        <f t="shared" si="0"/>
-        <v>5600</v>
+        <f>SUM(D8:O8)</f>
+        <v>6700</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1000,68 +1017,70 @@
       <c r="J9" s="14">
         <v>200</v>
       </c>
-      <c r="K9" s="2"/>
+      <c r="K9" s="2">
+        <v>100</v>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" s="3">
-        <f t="shared" si="0"/>
-        <v>2900</v>
+        <f>SUM(D9:O9)</f>
+        <v>3000</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D10" s="12">
-        <f t="shared" ref="D10:O10" si="1">SUM(D3:D9)</f>
+        <f>SUM(D3:D9)</f>
         <v>23500</v>
       </c>
       <c r="E10" s="12">
-        <f t="shared" si="1"/>
+        <f>SUM(E3:E9)</f>
         <v>30900</v>
       </c>
       <c r="F10" s="12">
-        <f t="shared" si="1"/>
+        <f>SUM(F3:F9)</f>
         <v>20700</v>
       </c>
       <c r="G10" s="12">
-        <f t="shared" si="1"/>
+        <f>SUM(G3:G9)</f>
         <v>15600</v>
       </c>
       <c r="H10" s="12">
-        <f t="shared" si="1"/>
+        <f>SUM(H3:H9)</f>
         <v>42900</v>
       </c>
       <c r="I10" s="12">
-        <f t="shared" si="1"/>
+        <f>SUM(I3:I9)</f>
         <v>28200</v>
       </c>
       <c r="J10" s="12">
-        <f t="shared" si="1"/>
+        <f>SUM(J3:J9)</f>
         <v>30200</v>
       </c>
       <c r="K10" s="12">
-        <f t="shared" si="1"/>
+        <f>SUM(K3:K9)</f>
+        <v>33200</v>
+      </c>
+      <c r="L10" s="12">
+        <f>SUM(L3:L9)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="12">
-        <f t="shared" si="1"/>
+      <c r="M10" s="12">
+        <f>SUM(M3:M9)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="12">
-        <f t="shared" si="1"/>
+      <c r="N10" s="12">
+        <f>SUM(N3:N9)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="12">
-        <f t="shared" si="1"/>
+      <c r="O10" s="12">
+        <f>SUM(O3:O9)</f>
         <v>0</v>
       </c>
-      <c r="O10" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="P10" s="13">
-        <f t="shared" si="0"/>
-        <v>192000</v>
+        <f>SUM(D10:O10)</f>
+        <v>225200</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -1182,7 +1201,7 @@
         <v>12700</v>
       </c>
       <c r="P19" s="3">
-        <f t="shared" ref="P19:P26" si="2">SUM(D19:O19)</f>
+        <f t="shared" ref="P19:P26" si="0">SUM(D19:O19)</f>
         <v>98700</v>
       </c>
       <c r="S19" s="2"/>
@@ -1234,7 +1253,7 @@
         <v>10000</v>
       </c>
       <c r="P20" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>96500</v>
       </c>
       <c r="S20" s="2"/>
@@ -1286,7 +1305,7 @@
         <v>3600</v>
       </c>
       <c r="P21" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>39000</v>
       </c>
       <c r="S21" s="2"/>
@@ -1338,7 +1357,7 @@
         <v>3400</v>
       </c>
       <c r="P22" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>33000</v>
       </c>
       <c r="S22" s="2"/>
@@ -1390,7 +1409,7 @@
         <v>1700</v>
       </c>
       <c r="P23" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>12600</v>
       </c>
     </row>
@@ -1439,7 +1458,7 @@
         <v>1300</v>
       </c>
       <c r="P24" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>9700</v>
       </c>
       <c r="S24" s="2"/>
@@ -1491,62 +1510,62 @@
         <v>700</v>
       </c>
       <c r="P25" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>7800</v>
       </c>
       <c r="S25" s="2"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D26" s="12">
-        <f t="shared" ref="D26:O26" si="3">SUM(D19:D25)</f>
+        <f t="shared" ref="D26:O26" si="1">SUM(D19:D25)</f>
         <v>33200</v>
       </c>
       <c r="E26" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>23900</v>
       </c>
       <c r="F26" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>23100</v>
       </c>
       <c r="G26" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>22600</v>
       </c>
       <c r="H26" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>13400</v>
       </c>
       <c r="I26" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>21600</v>
       </c>
       <c r="J26" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>15900</v>
       </c>
       <c r="K26" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>14400</v>
       </c>
       <c r="L26" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>44300</v>
       </c>
       <c r="M26" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>40300</v>
       </c>
       <c r="N26" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>11200</v>
       </c>
       <c r="O26" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>33400</v>
       </c>
       <c r="P26" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>297300</v>
       </c>
     </row>
@@ -1668,7 +1687,7 @@
         <v>8600</v>
       </c>
       <c r="P35" s="3">
-        <f t="shared" ref="P35:P42" si="4">SUM(D35:O35)</f>
+        <f t="shared" ref="P35:P42" si="2">SUM(D35:O35)</f>
         <v>93600</v>
       </c>
     </row>
@@ -1719,7 +1738,7 @@
         <v>7900</v>
       </c>
       <c r="P36" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>92600</v>
       </c>
     </row>
@@ -1770,7 +1789,7 @@
         <v>2900</v>
       </c>
       <c r="P37" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>42400</v>
       </c>
     </row>
@@ -1821,7 +1840,7 @@
         <v>3700</v>
       </c>
       <c r="P38" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>38700</v>
       </c>
     </row>
@@ -1870,7 +1889,7 @@
         <v>1800</v>
       </c>
       <c r="P39" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>20200</v>
       </c>
     </row>
@@ -1909,7 +1928,7 @@
         <v>800</v>
       </c>
       <c r="P40" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>5100</v>
       </c>
     </row>
@@ -1948,61 +1967,61 @@
         <v>700</v>
       </c>
       <c r="P41" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>3400</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D42" s="12">
-        <f t="shared" ref="D42:O42" si="5">SUM(D35:D41)</f>
+        <f t="shared" ref="D42:O42" si="3">SUM(D35:D41)</f>
         <v>30000</v>
       </c>
       <c r="E42" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>20100</v>
       </c>
       <c r="F42" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>21600</v>
       </c>
       <c r="G42" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>27600</v>
       </c>
       <c r="H42" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>18200</v>
       </c>
       <c r="I42" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>24500</v>
       </c>
       <c r="J42" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>15800</v>
       </c>
       <c r="K42" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>42100</v>
       </c>
       <c r="L42" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>18900</v>
       </c>
       <c r="M42" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>16400</v>
       </c>
       <c r="N42" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>34400</v>
       </c>
       <c r="O42" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>26400</v>
       </c>
       <c r="P42" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>296000</v>
       </c>
     </row>
